--- a/Assets/StreamingAssets/Excel/ProcessData.xlsx
+++ b/Assets/StreamingAssets/Excel/ProcessData.xlsx
@@ -1,28 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA61BB3E-FE96-4E4A-9C31-3BC54970993E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -155,9 +148,6 @@
     <t>&gt;=4</t>
   </si>
   <si>
-    <t>磁性触手</t>
-  </si>
-  <si>
     <t>钢材</t>
   </si>
   <si>
@@ -173,9 +163,6 @@
     <t>玻璃</t>
   </si>
   <si>
-    <t>&gt;=13</t>
-  </si>
-  <si>
     <t>玻璃沙</t>
   </si>
   <si>
@@ -183,19 +170,21 @@
   </si>
   <si>
     <t>珊瑚</t>
+  </si>
+  <si>
+    <t>&gt;=12</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁性触手+熟触手</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -221,352 +210,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -574,255 +241,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -838,90 +263,162 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color theme="1"/>
       </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -932,7 +429,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -960,154 +457,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1226,7 +609,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1345,28 +728,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.6761904761905" style="1"/>
-    <col min="2" max="2" width="8.76190476190476" customWidth="1"/>
-    <col min="3" max="3" width="12.8095238095238" style="1" customWidth="1"/>
-    <col min="4" max="12" width="8.76190476190476" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.8095238095238" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.76190476190476" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.8095238095238" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.76190476190476" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.8095238095238" style="1" customWidth="1"/>
-    <col min="18" max="18" width="8.76190476190476" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" style="1"/>
+    <col min="2" max="2" width="8.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" style="1" customWidth="1"/>
+    <col min="4" max="12" width="8.77734375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.77734375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.77734375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.77734375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12" spans="1:18">
+    <row r="1" spans="1:18" ht="12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1422,7 +805,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:18">
+    <row r="2" spans="1:18" ht="13.8">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -1478,7 +861,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:18">
+    <row r="3" spans="1:18" ht="13.8">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
@@ -1534,7 +917,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:18">
+    <row r="4" spans="1:18" ht="13.8">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1590,7 +973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:18">
+    <row r="5" spans="1:18" ht="13.8">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1646,7 +1029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="14.25" spans="1:18">
+    <row r="6" spans="1:18" ht="13.8">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
@@ -1702,7 +1085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:18">
+    <row r="7" spans="1:18" ht="13.8">
       <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
@@ -1758,7 +1141,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:18">
+    <row r="8" spans="1:18" ht="13.8">
       <c r="A8" s="2" t="s">
         <v>38</v>
       </c>
@@ -1814,7 +1197,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:18">
+    <row r="9" spans="1:18" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
@@ -1870,7 +1253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:18">
+    <row r="10" spans="1:18" ht="13.8">
       <c r="A10" s="2" t="s">
         <v>40</v>
       </c>
@@ -1907,8 +1290,8 @@
       <c r="L10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>42</v>
+      <c r="M10" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>24</v>
@@ -1926,18 +1309,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" ht="12" spans="1:18">
+    <row r="11" spans="1:18" ht="12">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>21</v>
@@ -1970,7 +1353,7 @@
         <v>24</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>24</v>
@@ -1982,18 +1365,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" ht="12" spans="1:18">
+    <row r="12" spans="1:18" ht="12">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -2020,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>26</v>
@@ -2038,18 +1421,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="12" spans="1:18">
+    <row r="13" spans="1:18" ht="12">
       <c r="A13" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -2076,7 +1459,7 @@
         <v>21</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>26</v>
@@ -2095,7 +1478,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Excel/ProcessData.xlsx
+++ b/Assets/StreamingAssets/Excel/ProcessData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unity工程文件E盘\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA61BB3E-FE96-4E4A-9C31-3BC54970993E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAF3F4A-4475-4AED-9589-329CBABD75B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="66">
   <si>
     <t>卡牌ID</t>
   </si>
@@ -118,66 +118,124 @@
     <t>肉排</t>
   </si>
   <si>
+    <t>炸虫串</t>
+  </si>
+  <si>
+    <t>海爬虫+熟海爬虫</t>
+  </si>
+  <si>
+    <t>贝类刺身</t>
+  </si>
+  <si>
+    <t>常温</t>
+  </si>
+  <si>
+    <t>鱼汤</t>
+  </si>
+  <si>
+    <t>厨房恶物</t>
+  </si>
+  <si>
+    <t>白灼触手</t>
+  </si>
+  <si>
+    <t>&gt;=4</t>
+  </si>
+  <si>
+    <t>钢材</t>
+  </si>
+  <si>
+    <t>高温</t>
+  </si>
+  <si>
+    <t>&gt;=12</t>
+  </si>
+  <si>
+    <t>废金属</t>
+  </si>
+  <si>
+    <t>玻璃</t>
+  </si>
+  <si>
+    <t>玻璃沙</t>
+  </si>
+  <si>
+    <t>石砖</t>
+  </si>
+  <si>
+    <t>珊瑚</t>
+  </si>
+  <si>
+    <t>&gt;=12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁性触手+熟触手</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶臭度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>蠕动盛宴</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;=4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>常温</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;=14</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已处理的海蜇皮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;=1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>坚果酥</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>低温+中温+高温</t>
-  </si>
-  <si>
-    <t>炸虫串</t>
-  </si>
-  <si>
-    <t>海爬虫+熟海爬虫</t>
-  </si>
-  <si>
-    <t>贝类刺身</t>
-  </si>
-  <si>
-    <t>常温</t>
-  </si>
-  <si>
-    <t>&gt;=14</t>
-  </si>
-  <si>
-    <t>鱼汤</t>
-  </si>
-  <si>
-    <t>厨房恶物</t>
-  </si>
-  <si>
-    <t>白灼触手</t>
-  </si>
-  <si>
-    <t>&gt;=4</t>
-  </si>
-  <si>
-    <t>钢材</t>
-  </si>
-  <si>
-    <t>高温</t>
-  </si>
-  <si>
-    <t>&gt;=12</t>
-  </si>
-  <si>
-    <t>废金属</t>
-  </si>
-  <si>
-    <t>玻璃</t>
-  </si>
-  <si>
-    <t>玻璃沙</t>
-  </si>
-  <si>
-    <t>石砖</t>
-  </si>
-  <si>
-    <t>珊瑚</t>
-  </si>
-  <si>
-    <t>&gt;=12</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁性触手+熟触手</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;=8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>菱果肉+烤菱果肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;=2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水果布丁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>==0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>凉拌海蜇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -204,12 +262,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -219,6 +271,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -260,7 +319,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -734,22 +793,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="1"/>
     <col min="2" max="2" width="8.77734375" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" style="1" customWidth="1"/>
-    <col min="4" max="12" width="8.77734375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.77734375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.77734375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.77734375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.77734375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.77734375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" style="1" customWidth="1"/>
+    <col min="4" max="13" width="8.77734375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.77734375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.77734375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12">
+    <row r="1" spans="1:19" ht="12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -786,26 +845,29 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="13.8">
+    <row r="2" spans="1:19" ht="13.8">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -843,14 +905,14 @@
         <v>21</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="P2" s="1" t="s">
         <v>21</v>
       </c>
@@ -860,8 +922,11 @@
       <c r="R2" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="S2" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="13.8">
+    <row r="3" spans="1:19" ht="13.8">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
@@ -916,8 +981,11 @@
       <c r="R3" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="S3" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" ht="13.8">
+    <row r="4" spans="1:19" ht="13.8">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -972,19 +1040,22 @@
       <c r="R4" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="S4" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" ht="13.8">
+    <row r="5" spans="1:19" ht="13.8">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
+      <c r="C5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>21</v>
@@ -1028,10 +1099,13 @@
       <c r="R5" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="S5" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" ht="13.8">
+    <row r="6" spans="1:19" ht="13.8">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -1039,8 +1113,8 @@
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>20</v>
+      <c r="D6" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>21</v>
@@ -1067,36 +1141,39 @@
         <v>21</v>
       </c>
       <c r="M6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="13.8">
+      <c r="A7" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="13.8">
-      <c r="A7" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="B7">
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>21</v>
@@ -1140,16 +1217,19 @@
       <c r="R7" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="S7" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" ht="13.8">
+    <row r="8" spans="1:19" ht="13.8">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>32</v>
+      <c r="C8" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>20</v>
@@ -1196,16 +1276,19 @@
       <c r="R8" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="S8" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="9" spans="1:18" ht="18" customHeight="1">
+    <row r="9" spans="1:19" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
+      <c r="C9" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>21</v>
@@ -1252,10 +1335,13 @@
       <c r="R9" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="S9" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="10" spans="1:18" ht="13.8">
+    <row r="10" spans="1:19" ht="13.8">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -1264,13 +1350,13 @@
         <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>30</v>
+      <c r="F10" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>21</v>
@@ -1290,15 +1376,15 @@
       <c r="L10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="N10" s="1" t="s">
+      <c r="M10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="P10" s="1" t="s">
         <v>21</v>
       </c>
@@ -1308,75 +1394,81 @@
       <c r="R10" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="S10" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="11" spans="1:18" ht="12">
+    <row r="11" spans="1:19" ht="12">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="12">
+      <c r="A12" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="12">
-      <c r="A12" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="B12">
         <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>50</v>
+        <v>41</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -1403,14 +1495,14 @@
         <v>21</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="N12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="P12" s="1" t="s">
         <v>21</v>
       </c>
@@ -1420,19 +1512,22 @@
       <c r="R12" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="S12" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="13" spans="1:18" ht="12">
+    <row r="13" spans="1:19" ht="12">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>50</v>
+        <v>41</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -1459,14 +1554,14 @@
         <v>21</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="P13" s="1" t="s">
         <v>21</v>
       </c>
@@ -1475,10 +1570,249 @@
       </c>
       <c r="R13" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="18" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="18" customHeight="1">
+      <c r="A15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="18" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="18" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>